--- a/fixtures/sml/cell/negative.xlsx
+++ b/fixtures/sml/cell/negative.xlsx
@@ -10,8 +10,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
-    <row r="0">
-      <c r="0">
+    <row r="1">
+      <c r="A1">
         <v>-273.15</v>
       </c>
     </row>
